--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_F536BBD8257D76D6946F7F09A986548284187988" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADD81681-96C9-47B8-AFF0-6BAD08F8B059}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_F536BBD8257D76D6946F7F09A986548284187988" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0625178-D2D5-4367-B451-F13276C266A8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="86">
   <si>
     <t>A卡池</t>
   </si>
@@ -290,6 +290,10 @@
   </si>
   <si>
     <t>转着圈射弹幕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -377,6 +381,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -870,6 +878,9 @@
       <c r="B18" t="s">
         <v>19</v>
       </c>
+      <c r="C18" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="D18" t="s">
         <v>6</v>
       </c>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_F536BBD8257D76D6946F7F09A986548284187988" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0625178-D2D5-4367-B451-F13276C266A8}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_F536BBD8257D76D6946F7F09A986548284187988" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{670EF593-E46B-4438-892D-F77BCCD25334}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="91">
   <si>
     <t>A卡池</t>
   </si>
@@ -294,6 +294,26 @@
   </si>
   <si>
     <t>消耗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个弹幕13点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每下25点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每下20点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每下17点</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -933,6 +953,9 @@
       <c r="C32" t="s">
         <v>48</v>
       </c>
+      <c r="D32" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="E32" t="s">
         <v>49</v>
       </c>
@@ -962,6 +985,9 @@
       <c r="C33">
         <v>5</v>
       </c>
+      <c r="D33" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="E33" s="1" t="s">
         <v>56</v>
       </c>
@@ -988,6 +1014,9 @@
       <c r="C34">
         <v>9</v>
       </c>
+      <c r="D34" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="I34" t="s">
         <v>62</v>
       </c>
@@ -1002,6 +1031,9 @@
       <c r="C35">
         <v>4</v>
       </c>
+      <c r="D35" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="E35" s="1" t="s">
         <v>63</v>
       </c>
@@ -1028,6 +1060,9 @@
       <c r="C36">
         <v>5</v>
       </c>
+      <c r="D36" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="G36" s="1" t="s">
         <v>68</v>
       </c>
@@ -1042,6 +1077,9 @@
       <c r="C37">
         <v>8</v>
       </c>
+      <c r="D37" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="E37" s="1" t="s">
         <v>69</v>
       </c>
@@ -1071,6 +1109,9 @@
       <c r="C38">
         <v>11</v>
       </c>
+      <c r="D38" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="E38" s="1" t="s">
         <v>63</v>
       </c>
@@ -1091,6 +1132,9 @@
       <c r="C39" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="D39" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="E39" s="1" t="s">
         <v>69</v>
       </c>
@@ -1125,6 +1169,9 @@
       </c>
       <c r="C41" s="3" t="s">
         <v>83</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>84</v>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_F536BBD8257D76D6946F7F09A986548284187988" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{670EF593-E46B-4438-892D-F77BCCD25334}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_F536BBD8257D76D6946F7F09A986548284187988" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52063A05-478E-441D-8D78-2080D0C60E42}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -301,10 +301,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>每个弹幕13点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>每下25点</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -314,6 +310,10 @@
   </si>
   <si>
     <t>每下17点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个弹幕6点</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -986,7 +986,7 @@
         <v>5</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>56</v>
@@ -1015,7 +1015,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s">
         <v>62</v>
@@ -1032,7 +1032,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>63</v>
@@ -1061,7 +1061,7 @@
         <v>5</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>68</v>
@@ -1078,7 +1078,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>69</v>
@@ -1110,7 +1110,7 @@
         <v>11</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>63</v>
@@ -1133,7 +1133,7 @@
         <v>77</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>69</v>
@@ -1171,7 +1171,7 @@
         <v>83</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>84</v>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_F536BBD8257D76D6946F7F09A986548284187988" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52063A05-478E-441D-8D78-2080D0C60E42}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_F536BBD8257D76D6946F7F09A986548284187988" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B3BCC4E-739E-46DE-ACCF-2399752ED519}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>A卡池</t>
   </si>
@@ -99,12 +99,6 @@
     <t>断裂</t>
   </si>
   <si>
-    <t>连线恢复前，玩家可以穿墙</t>
-  </si>
-  <si>
-    <t>穿墙</t>
-  </si>
-  <si>
     <t>B卡池</t>
   </si>
   <si>
@@ -314,6 +308,18 @@
   </si>
   <si>
     <t>每个弹幕6点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连线恢复前，玩家移速增加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移速增加一倍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加速</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -795,16 +801,19 @@
       <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" t="s">
-        <v>22</v>
+      <c r="D8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -815,10 +824,10 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -826,13 +835,13 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" t="s">
         <v>26</v>
-      </c>
-      <c r="E13" t="s">
-        <v>27</v>
-      </c>
-      <c r="J13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -840,13 +849,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -854,13 +863,13 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" t="s">
         <v>31</v>
-      </c>
-      <c r="E15" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -868,13 +877,13 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" t="s">
         <v>34</v>
-      </c>
-      <c r="E16" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -882,16 +891,16 @@
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -899,7 +908,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
@@ -907,77 +916,77 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>49</v>
       </c>
-      <c r="F32" t="s">
+      <c r="H32" t="s">
         <v>50</v>
       </c>
-      <c r="G32" t="s">
+      <c r="I32" t="s">
         <v>51</v>
       </c>
-      <c r="H32" t="s">
+      <c r="J32" t="s">
         <v>52</v>
-      </c>
-      <c r="I32" t="s">
-        <v>53</v>
-      </c>
-      <c r="J32" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -986,27 +995,27 @@
         <v>5</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="H33" t="s">
         <v>57</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="J33" t="s">
         <v>58</v>
-      </c>
-      <c r="H33" t="s">
-        <v>59</v>
-      </c>
-      <c r="J33" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -1015,15 +1024,15 @@
         <v>9</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I34" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -1032,27 +1041,27 @@
         <v>4</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="H35" t="s">
         <v>64</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="J35" t="s">
         <v>65</v>
-      </c>
-      <c r="H35" t="s">
-        <v>66</v>
-      </c>
-      <c r="J35" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1061,15 +1070,15 @@
         <v>5</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -1078,30 +1087,30 @@
         <v>8</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" t="s">
         <v>69</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="I37" t="s">
         <v>70</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
         <v>71</v>
-      </c>
-      <c r="I37" t="s">
-        <v>72</v>
-      </c>
-      <c r="J37" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1110,48 +1119,48 @@
         <v>11</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H39" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="I39" t="s">
         <v>78</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" t="s">
         <v>79</v>
-      </c>
-      <c r="I39" t="s">
-        <v>80</v>
-      </c>
-      <c r="J39" t="s">
-        <v>81</v>
       </c>
       <c r="N39">
         <f>F3</f>
@@ -1160,7 +1169,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -1168,13 +1177,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_F536BBD8257D76D6946F7F09A986548284187988" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B3BCC4E-739E-46DE-ACCF-2399752ED519}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="8625" windowHeight="8820"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
   <si>
     <t>A卡池</t>
   </si>
@@ -87,7 +81,7 @@
     <t>屏幕上所有怪物往左推</t>
   </si>
   <si>
-    <t>清场</t>
+    <t>群体位移</t>
   </si>
   <si>
     <t>消耗，恢复生成x3，断裂</t>
@@ -99,6 +93,15 @@
     <t>断裂</t>
   </si>
   <si>
+    <t>移速增加一倍</t>
+  </si>
+  <si>
+    <t>连线恢复前，玩家移速增加</t>
+  </si>
+  <si>
+    <t>加速</t>
+  </si>
+  <si>
     <t>B卡池</t>
   </si>
   <si>
@@ -177,6 +180,9 @@
     <t>血量</t>
   </si>
   <si>
+    <t>伤害</t>
+  </si>
+  <si>
     <t>体型</t>
   </si>
   <si>
@@ -198,6 +204,9 @@
     <t>第一个任务点前</t>
   </si>
   <si>
+    <t>每下17点</t>
+  </si>
+  <si>
     <t>玩家0.6倍</t>
   </si>
   <si>
@@ -216,9 +225,15 @@
     <t>第二个任务点前</t>
   </si>
   <si>
+    <t>每下20点</t>
+  </si>
+  <si>
     <t>玩家被打到后，给玩家减速</t>
   </si>
   <si>
+    <t>每个弹幕6点</t>
+  </si>
+  <si>
     <t>玩家1.5倍</t>
   </si>
   <si>
@@ -237,6 +252,9 @@
     <t>同上，改成两条平行的弹幕</t>
   </si>
   <si>
+    <t>每下25点</t>
+  </si>
+  <si>
     <t>玩家大小</t>
   </si>
   <si>
@@ -280,54 +298,22 @@
   </si>
   <si>
     <t>同上</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>转着圈射弹幕</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每下25点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每下20点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每下17点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每个弹幕6点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>连线恢复前，玩家移速增加</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>移速增加一倍</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>加速</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -343,29 +329,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -373,9 +675,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -383,34 +927,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -685,14 +1269,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
     <col min="3" max="3" width="21.625" customWidth="1"/>
@@ -702,12 +1286,12 @@
     <col min="9" max="9" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -724,7 +1308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="B3">
         <v>1</v>
       </c>
@@ -738,7 +1322,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4">
         <v>2</v>
       </c>
@@ -752,7 +1336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="5" ht="28.5" spans="1:10">
       <c r="B5">
         <v>3</v>
       </c>
@@ -766,7 +1350,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="B6">
         <v>4</v>
       </c>
@@ -783,7 +1367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7">
         <v>5</v>
       </c>
@@ -794,7 +1378,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8">
         <v>6</v>
       </c>
@@ -802,21 +1386,21 @@
         <v>20</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12">
         <v>7</v>
       </c>
@@ -824,169 +1408,169 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="B17">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="C21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="C22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="C23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="C24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="C25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="C26" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G32" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H32" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I32" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -995,27 +1579,27 @@
         <v>5</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H33" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -1024,15 +1608,15 @@
         <v>9</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="I34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -1041,27 +1625,27 @@
         <v>4</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H35" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
         <v>64</v>
-      </c>
-      <c r="J35" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>59</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1070,15 +1654,15 @@
         <v>5</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -1087,30 +1671,30 @@
         <v>8</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I37" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="J37" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1119,75 +1703,75 @@
         <v>11</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J39" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N39">
         <f>F3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="B41">
         <v>8</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="8625" windowHeight="8820"/>
+    <workbookView windowWidth="23145" windowHeight="8955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -313,14 +313,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -793,137 +786,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -932,9 +925,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1385,13 +1375,13 @@
       <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1491,7 +1481,7 @@
       <c r="B18" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D18" t="s">
@@ -1546,7 +1536,7 @@
       <c r="C32" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E32" t="s">
@@ -1578,7 +1568,7 @@
       <c r="C33">
         <v>5</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -1607,7 +1597,7 @@
       <c r="C34">
         <v>9</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="1" t="s">
         <v>65</v>
       </c>
       <c r="I34" t="s">
@@ -1624,7 +1614,7 @@
       <c r="C35">
         <v>4</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -1653,7 +1643,7 @@
       <c r="C36">
         <v>5</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -1670,7 +1660,7 @@
       <c r="C37">
         <v>8</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="1" t="s">
         <v>74</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -1702,7 +1692,7 @@
       <c r="C38">
         <v>11</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="1" t="s">
         <v>74</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -1725,7 +1715,7 @@
       <c r="C39" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -1760,13 +1750,13 @@
       <c r="B41">
         <v>8</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="1" t="s">
         <v>90</v>
       </c>
     </row>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -126,7 +126,7 @@
     <t>群体冻结</t>
   </si>
   <si>
-    <t>消耗，恢复生成</t>
+    <t>断裂·，消耗，恢复生成</t>
   </si>
   <si>
     <t>使随机一张手牌失去消耗</t>
@@ -1465,7 +1465,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="90">
   <si>
     <t>A卡池</t>
   </si>
@@ -65,17 +65,13 @@
     <t>撞击怪物</t>
   </si>
   <si>
-    <t>怪物仍然造成一次伤害
-做一个弹幕从肉体飞到敌人的动画</t>
-  </si>
-  <si>
-    <t>双方下一张牌打出前，消灭攻击肉体的怪物</t>
+    <t>消耗</t>
+  </si>
+  <si>
+    <t>断裂前，怪物攻击肉体后，对自身造成等量伤害</t>
   </si>
   <si>
     <t>反杀怪物</t>
-  </si>
-  <si>
-    <t>消耗</t>
   </si>
   <si>
     <t>屏幕上所有怪物往左推</t>
@@ -1326,13 +1322,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="28.5" spans="1:10">
+    <row r="5" spans="1:10">
       <c r="B5">
         <v>3</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
+      <c r="D5" s="2"/>
       <c r="E5" t="s">
         <v>13</v>
       </c>
@@ -1345,16 +1342,16 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
         <v>16</v>
-      </c>
-      <c r="J6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1362,10 +1359,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
         <v>18</v>
-      </c>
-      <c r="J7" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1373,21 +1370,21 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1398,10 +1395,10 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" t="s">
         <v>25</v>
-      </c>
-      <c r="J12" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1409,13 +1406,13 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
         <v>27</v>
       </c>
-      <c r="E13" t="s">
+      <c r="J13" t="s">
         <v>28</v>
-      </c>
-      <c r="J13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1423,13 +1420,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" t="s">
         <v>30</v>
-      </c>
-      <c r="J14" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1437,13 +1434,13 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
         <v>32</v>
       </c>
-      <c r="E15" t="s">
+      <c r="J15" t="s">
         <v>33</v>
-      </c>
-      <c r="J15" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1451,13 +1448,13 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
         <v>35</v>
       </c>
-      <c r="E16" t="s">
+      <c r="J16" t="s">
         <v>36</v>
-      </c>
-      <c r="J16" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1465,24 +1462,24 @@
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
       <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" t="s">
         <v>38</v>
-      </c>
-      <c r="J17" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="B18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
@@ -1490,77 +1487,77 @@
     </row>
     <row r="21" spans="1:10">
       <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
         <v>40</v>
-      </c>
-      <c r="D21" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="C22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="C23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="C24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="C25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="C26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" t="s">
         <v>50</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>51</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>52</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>53</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>54</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>55</v>
-      </c>
-      <c r="J32" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -1569,27 +1566,27 @@
         <v>5</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="H33" t="s">
         <v>61</v>
       </c>
-      <c r="H33" t="s">
+      <c r="J33" t="s">
         <v>62</v>
-      </c>
-      <c r="J33" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -1598,15 +1595,15 @@
         <v>9</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I34" t="s">
         <v>65</v>
-      </c>
-      <c r="I34" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -1615,27 +1612,27 @@
         <v>4</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="H35" t="s">
         <v>70</v>
       </c>
-      <c r="H35" t="s">
+      <c r="J35" t="s">
         <v>71</v>
-      </c>
-      <c r="J35" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1644,15 +1641,15 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -1661,30 +1658,30 @@
         <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" t="s">
         <v>76</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>77</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>78</v>
-      </c>
-      <c r="J37" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1693,48 +1690,48 @@
         <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="H39" t="s">
         <v>84</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>85</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>86</v>
-      </c>
-      <c r="J39" t="s">
-        <v>87</v>
       </c>
       <c r="N39">
         <f>F3</f>
@@ -1743,7 +1740,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -1751,13 +1748,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
   <si>
     <t>A卡池</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>反杀怪物</t>
+  </si>
+  <si>
+    <t>消耗，恢复生成</t>
   </si>
   <si>
     <t>屏幕上所有怪物往左推</t>
@@ -1342,16 +1345,16 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1359,10 +1362,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1370,21 +1373,21 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1395,10 +1398,10 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1406,13 +1409,13 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1420,13 +1423,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1434,13 +1437,13 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1448,13 +1451,13 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1462,21 +1465,21 @@
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="B18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>12</v>
@@ -1487,77 +1490,77 @@
     </row>
     <row r="21" spans="1:10">
       <c r="C21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="C22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="C23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="C24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="C25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="C26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -1566,27 +1569,27 @@
         <v>5</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -1595,15 +1598,15 @@
         <v>9</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -1612,27 +1615,27 @@
         <v>4</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1641,15 +1644,15 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -1658,30 +1661,30 @@
         <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1690,48 +1693,48 @@
         <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N39">
         <f>F3</f>
@@ -1740,7 +1743,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -1748,13 +1751,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>A卡池</t>
   </si>
@@ -83,7 +83,7 @@
     <t>群体位移</t>
   </si>
   <si>
-    <t>消耗，恢复生成x3，断裂</t>
+    <t>消耗，恢复生成x2，断裂</t>
   </si>
   <si>
     <t>恢复</t>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>恢复不是消耗</t>
+  </si>
+  <si>
+    <t>玩家的攻击可以移除弹幕</t>
   </si>
   <si>
     <t>敌人</t>
@@ -1521,46 +1524,51 @@
         <v>46</v>
       </c>
     </row>
+    <row r="27" spans="1:10">
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+    </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -1569,27 +1577,27 @@
         <v>5</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -1598,15 +1606,15 @@
         <v>9</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -1615,27 +1623,27 @@
         <v>4</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1644,15 +1652,15 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -1661,30 +1669,30 @@
         <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1693,48 +1701,48 @@
         <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N39">
         <f>F3</f>
@@ -1743,7 +1751,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -1751,13 +1759,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
   <si>
     <t>A卡池</t>
   </si>
@@ -134,10 +134,7 @@
     <t>优化手牌</t>
   </si>
   <si>
-    <t>放到后面卡池</t>
-  </si>
-  <si>
-    <t>连线断裂前，你无法出牌。另一位玩家CD为0.5秒</t>
+    <t>连线断裂前，你无法出牌。另一位玩家CD为0秒</t>
   </si>
   <si>
     <t>集中火力</t>
@@ -1453,14 +1450,11 @@
       <c r="B16">
         <v>11</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>35</v>
       </c>
-      <c r="E16" t="s">
+      <c r="J16" t="s">
         <v>36</v>
-      </c>
-      <c r="J16" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1474,10 +1468,10 @@
         <v>6</v>
       </c>
       <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" t="s">
         <v>38</v>
-      </c>
-      <c r="J17" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1493,82 +1487,82 @@
     </row>
     <row r="21" spans="1:10">
       <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
         <v>40</v>
-      </c>
-      <c r="D21" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="C22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="C23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="C24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="C25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="C26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="C27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" t="s">
         <v>51</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>52</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>53</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>54</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>55</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>56</v>
-      </c>
-      <c r="J32" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -1577,27 +1571,27 @@
         <v>5</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="H33" t="s">
         <v>62</v>
       </c>
-      <c r="H33" t="s">
+      <c r="J33" t="s">
         <v>63</v>
-      </c>
-      <c r="J33" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -1606,15 +1600,15 @@
         <v>9</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34" t="s">
         <v>66</v>
-      </c>
-      <c r="I34" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -1623,27 +1617,27 @@
         <v>4</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="H35" t="s">
         <v>71</v>
       </c>
-      <c r="H35" t="s">
+      <c r="J35" t="s">
         <v>72</v>
-      </c>
-      <c r="J35" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1652,15 +1646,15 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -1669,30 +1663,30 @@
         <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" t="s">
         <v>77</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>78</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>79</v>
-      </c>
-      <c r="J37" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1701,48 +1695,48 @@
         <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="H39" t="s">
         <v>85</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>86</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>87</v>
-      </c>
-      <c r="J39" t="s">
-        <v>88</v>
       </c>
       <c r="N39">
         <f>F3</f>
@@ -1751,7 +1745,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -1759,13 +1753,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>A卡池</t>
   </si>
@@ -134,7 +134,10 @@
     <t>优化手牌</t>
   </si>
   <si>
-    <t>连线断裂前，你无法出牌。另一位玩家CD为0秒</t>
+    <t>也就是CD为0秒</t>
+  </si>
+  <si>
+    <t>连线断裂前，你无法出牌。另一位玩家没有CD</t>
   </si>
   <si>
     <t>集中火力</t>
@@ -1450,11 +1453,14 @@
       <c r="B16">
         <v>11</v>
       </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1468,10 +1474,10 @@
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1487,82 +1493,82 @@
     </row>
     <row r="21" spans="1:10">
       <c r="C21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="C22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="C23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="C24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="C25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="C26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="C27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -1571,27 +1577,27 @@
         <v>5</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -1600,15 +1606,15 @@
         <v>9</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -1617,27 +1623,27 @@
         <v>4</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1646,15 +1652,15 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -1663,30 +1669,30 @@
         <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1695,48 +1701,48 @@
         <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N39">
         <f>F3</f>
@@ -1745,7 +1751,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -1753,13 +1759,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_CF42B8CE256D76DD782D776BA1A323038D8897D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F45EE68-A383-4D70-8AE1-8A5769FD1162}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="11_CF42B8CE256D76DD782D776BA1A323038D8897D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{591A9FF5-9E8B-47B9-944B-1B551644F995}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="93">
   <si>
     <t>A卡池</t>
   </si>
@@ -65,15 +65,9 @@
     <t>撞击怪物</t>
   </si>
   <si>
-    <t>消耗</t>
-  </si>
-  <si>
     <t>反杀怪物</t>
   </si>
   <si>
-    <t>消耗，恢复生成</t>
-  </si>
-  <si>
     <t>群体位移</t>
   </si>
   <si>
@@ -95,9 +89,6 @@
     <t>击退</t>
   </si>
   <si>
-    <t>断裂，消耗</t>
-  </si>
-  <si>
     <t>CD分配</t>
   </si>
   <si>
@@ -272,6 +263,10 @@
     <t>转着圈射弹幕</t>
   </si>
   <si>
+    <t>所有怪物往左推</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>击退所有怪物，消耗血量</t>
   </si>
   <si>
@@ -284,47 +279,53 @@
   </si>
   <si>
     <t>断裂时，你无法出牌。队友没有CD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>你可以撞伤怪物</t>
-  </si>
-  <si>
-    <t>消耗。恢复链接，回满血</t>
-  </si>
-  <si>
-    <t>消耗。获得一张恢复。你每有一张手牌，队友下一次伤害增加</t>
-  </si>
-  <si>
-    <t>消耗。断裂。获得一张恢复。一张消耗牌变为固定</t>
-  </si>
-  <si>
-    <t>消耗。断裂。断裂时，冻结怪物</t>
-  </si>
-  <si>
-    <t>消耗。断裂。你的CD翻倍，队友的CD减半</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>断裂。断裂时，移速增加</t>
   </si>
   <si>
-    <t>消耗。断裂。获得两张恢复</t>
-  </si>
-  <si>
-    <t>消耗。所有怪物往左推。获得一张恢复</t>
-  </si>
-  <si>
-    <t>消耗。反伤怪物，直到断裂</t>
-  </si>
-  <si>
-    <t>断裂·，消耗，恢复生成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗，恢复生成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗，恢复生成x2，断裂</t>
+    <t>初始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反伤怪物3秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得10点血量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断裂。玩家冷却加快10秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CD减少50%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断裂。断裂时，冻结怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断裂。变为上一张手牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>队友下一次伤害增加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始，增加1.5倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复牌：不在任何卡池：两个玩家开始时各持有一张：恢复链接，回满血</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -724,7 +725,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
@@ -738,7 +739,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J4" t="s">
         <v>9</v>
@@ -748,15 +749,13 @@
       <c r="B5">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="J5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -764,30 +763,28 @@
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
+        <v>79</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="J6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>5</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" t="s">
-        <v>90</v>
+      <c r="C7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -795,21 +792,21 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J8" t="s">
         <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -820,38 +817,41 @@
         <v>6</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>8</v>
       </c>
-      <c r="C13" t="s">
-        <v>20</v>
+      <c r="C13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>9</v>
       </c>
-      <c r="C14" t="s">
-        <v>20</v>
+      <c r="C14" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -859,13 +859,13 @@
         <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -873,127 +873,118 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>12</v>
       </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
-        <v>6</v>
+      <c r="D17" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" t="s">
-        <v>84</v>
-      </c>
+      <c r="E18" s="2"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C27" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C28" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" t="s">
         <v>37</v>
       </c>
-      <c r="D32" t="s">
+      <c r="G32" t="s">
         <v>38</v>
       </c>
-      <c r="E32" t="s">
+      <c r="H32" t="s">
         <v>39</v>
       </c>
-      <c r="F32" t="s">
+      <c r="I32" t="s">
         <v>40</v>
       </c>
-      <c r="G32" t="s">
+      <c r="J32" t="s">
         <v>41</v>
-      </c>
-      <c r="H32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32" t="s">
-        <v>43</v>
-      </c>
-      <c r="J32" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -1002,27 +993,27 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" t="s">
         <v>46</v>
       </c>
-      <c r="E33" t="s">
+      <c r="H33" t="s">
         <v>47</v>
       </c>
-      <c r="F33" t="s">
+      <c r="J33" t="s">
         <v>48</v>
-      </c>
-      <c r="G33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H33" t="s">
-        <v>50</v>
-      </c>
-      <c r="J33" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -1031,15 +1022,15 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I34" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -1048,27 +1039,27 @@
         <v>4</v>
       </c>
       <c r="D35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" t="s">
+        <v>54</v>
+      </c>
+      <c r="G35" t="s">
         <v>55</v>
       </c>
-      <c r="E35" t="s">
+      <c r="H35" t="s">
         <v>56</v>
       </c>
-      <c r="F35" t="s">
+      <c r="J35" t="s">
         <v>57</v>
-      </c>
-      <c r="G35" t="s">
-        <v>58</v>
-      </c>
-      <c r="H35" t="s">
-        <v>59</v>
-      </c>
-      <c r="J35" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1077,15 +1068,15 @@
         <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G36" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -1094,30 +1085,30 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" t="s">
+        <v>54</v>
+      </c>
+      <c r="G37" t="s">
+        <v>61</v>
+      </c>
+      <c r="H37" t="s">
         <v>62</v>
       </c>
-      <c r="E37" t="s">
+      <c r="I37" t="s">
         <v>63</v>
       </c>
-      <c r="F37" t="s">
-        <v>57</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="J37" t="s">
         <v>64</v>
-      </c>
-      <c r="H37" t="s">
-        <v>65</v>
-      </c>
-      <c r="I37" t="s">
-        <v>66</v>
-      </c>
-      <c r="J37" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1126,48 +1117,48 @@
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F38" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G38" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
       <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" t="s">
+        <v>66</v>
+      </c>
+      <c r="G39" t="s">
+        <v>69</v>
+      </c>
+      <c r="H39" t="s">
+        <v>70</v>
+      </c>
+      <c r="I39" t="s">
         <v>71</v>
       </c>
-      <c r="D39" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" t="s">
-        <v>63</v>
-      </c>
-      <c r="F39" t="s">
-        <v>69</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="J39" t="s">
         <v>72</v>
-      </c>
-      <c r="H39" t="s">
-        <v>73</v>
-      </c>
-      <c r="I39" t="s">
-        <v>74</v>
-      </c>
-      <c r="J39" t="s">
-        <v>75</v>
       </c>
       <c r="N39">
         <f>F3</f>
@@ -1176,7 +1167,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -1184,13 +1175,13 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D41" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G41" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="11_CF42B8CE256D76DD782D776BA1A323038D8897D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{591A9FF5-9E8B-47B9-944B-1B551644F995}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="11_CF42B8CE256D76DD782D776BA1A323038D8897D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB3CFBF6-9E44-4B24-AFDD-254E898AF2A8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="94">
   <si>
     <t>A卡池</t>
   </si>
@@ -77,9 +77,6 @@
     <t>断裂</t>
   </si>
   <si>
-    <t>移速增加一倍</t>
-  </si>
-  <si>
     <t>加速</t>
   </si>
   <si>
@@ -173,9 +170,6 @@
     <t>3秒一次</t>
   </si>
   <si>
-    <t>以自身为原点，半径为自身直径的圆</t>
-  </si>
-  <si>
     <t>近战，类似冲击波</t>
   </si>
   <si>
@@ -263,10 +257,6 @@
     <t>转着圈射弹幕</t>
   </si>
   <si>
-    <t>所有怪物往左推</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>击退所有怪物，消耗血量</t>
   </si>
   <si>
@@ -289,26 +279,10 @@
     <t>断裂。断裂时，移速增加</t>
   </si>
   <si>
-    <t>初始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反伤怪物3秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>获得10点血量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>断裂。玩家冷却加快10秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CD减少50%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>断裂。断裂时，冻结怪物</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -326,6 +300,38 @@
   </si>
   <si>
     <t>恢复牌：不在任何卡池：两个玩家开始时各持有一张：恢复链接，回满血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>近战</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始，推260像素</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移速翻倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断裂。所有怪物往左推</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断裂。玩家冷却加快</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反伤怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物攻击肉体后，对自己造成等量伤害。持续3秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CD减少50%，持续7秒</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -383,11 +389,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -724,8 +730,8 @@
       <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>78</v>
+      <c r="E3" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
@@ -738,21 +744,23 @@
       <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>81</v>
+      <c r="E4" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="J4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="2" t="s">
-        <v>84</v>
+      <c r="C5" s="1"/>
+      <c r="D5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="J5" t="s">
         <v>10</v>
@@ -762,14 +770,14 @@
       <c r="B6">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>76</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="J6" t="s">
         <v>11</v>
@@ -779,9 +787,9 @@
       <c r="B7">
         <v>5</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>85</v>
+      <c r="C7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="J7" t="s">
         <v>12</v>
@@ -794,19 +802,19 @@
       <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" t="s">
         <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -816,175 +824,175 @@
       <c r="D12" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>77</v>
+      <c r="E12" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>8</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>86</v>
+      <c r="C13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>9</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>88</v>
+      <c r="C14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>10</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>89</v>
+      <c r="C15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>11</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>79</v>
+      <c r="C16" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" t="s">
         <v>21</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J16" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>12</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>90</v>
+      <c r="D17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="J17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E18" s="2"/>
+      <c r="E18" s="1"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" t="s">
         <v>24</v>
-      </c>
-      <c r="D21" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="C28" s="2" t="s">
-        <v>92</v>
+      <c r="C28" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" t="s">
         <v>34</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>35</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>36</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>37</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>38</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>39</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>40</v>
-      </c>
-      <c r="J32" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -993,27 +1001,27 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" t="s">
         <v>43</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>44</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" t="s">
         <v>45</v>
       </c>
-      <c r="G33" t="s">
+      <c r="J33" t="s">
         <v>46</v>
-      </c>
-      <c r="H33" t="s">
-        <v>47</v>
-      </c>
-      <c r="J33" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -1022,15 +1030,15 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -1039,27 +1047,27 @@
         <v>4</v>
       </c>
       <c r="D35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" t="s">
         <v>52</v>
       </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>53</v>
       </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
         <v>54</v>
       </c>
-      <c r="G35" t="s">
+      <c r="J35" t="s">
         <v>55</v>
-      </c>
-      <c r="H35" t="s">
-        <v>56</v>
-      </c>
-      <c r="J35" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1068,15 +1076,15 @@
         <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -1085,30 +1093,30 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" t="s">
         <v>59</v>
       </c>
-      <c r="E37" t="s">
+      <c r="H37" t="s">
         <v>60</v>
       </c>
-      <c r="F37" t="s">
-        <v>54</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="I37" t="s">
         <v>61</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
         <v>62</v>
-      </c>
-      <c r="I37" t="s">
-        <v>63</v>
-      </c>
-      <c r="J37" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1117,48 +1125,48 @@
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E38" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G38" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
       <c r="C39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" t="s">
+        <v>67</v>
+      </c>
+      <c r="H39" t="s">
         <v>68</v>
       </c>
-      <c r="D39" t="s">
-        <v>52</v>
-      </c>
-      <c r="E39" t="s">
-        <v>60</v>
-      </c>
-      <c r="F39" t="s">
-        <v>66</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="I39" t="s">
         <v>69</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" t="s">
         <v>70</v>
-      </c>
-      <c r="I39" t="s">
-        <v>71</v>
-      </c>
-      <c r="J39" t="s">
-        <v>72</v>
       </c>
       <c r="N39">
         <f>F3</f>
@@ -1167,7 +1175,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -1175,13 +1183,13 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G41" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="11_CF42B8CE256D76DD782D776BA1A323038D8897D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB3CFBF6-9E44-4B24-AFDD-254E898AF2A8}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="11_CF42B8CE256D76DD782D776BA1A323038D8897D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA83C241-2766-4D9E-80D3-DEC01556DF9E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="95">
   <si>
     <t>A卡池</t>
   </si>
@@ -287,10 +287,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>断裂。变为上一张手牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>队友下一次伤害增加</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -332,6 +328,14 @@
   </si>
   <si>
     <t>CD减少50%，持续7秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肉体可以穿墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续7秒，还是有和其他东西的碰撞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -695,7 +699,7 @@
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
     <col min="3" max="3" width="21.625" customWidth="1"/>
-    <col min="4" max="4" width="28.75" customWidth="1"/>
+    <col min="4" max="4" width="35.125" customWidth="1"/>
     <col min="7" max="7" width="80.625" customWidth="1"/>
     <col min="8" max="8" width="20.25" customWidth="1"/>
     <col min="9" max="9" width="22.625" customWidth="1"/>
@@ -757,10 +761,10 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J5" t="s">
         <v>10</v>
@@ -774,10 +778,10 @@
         <v>76</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J6" t="s">
         <v>11</v>
@@ -803,7 +807,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>79</v>
@@ -839,10 +843,10 @@
         <v>76</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -866,11 +870,12 @@
       <c r="B15">
         <v>10</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>76</v>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -898,10 +903,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J17" t="s">
         <v>22</v>
@@ -950,7 +955,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -1010,7 +1015,7 @@
         <v>44</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s">
         <v>45</v>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="11_CF42B8CE256D76DD782D776BA1A323038D8897D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA83C241-2766-4D9E-80D3-DEC01556DF9E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23145" windowHeight="8955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="94">
   <si>
     <t>A卡池</t>
   </si>
@@ -56,25 +50,52 @@
     <t>初始</t>
   </si>
   <si>
+    <t>连线对怪物造成伤害</t>
+  </si>
+  <si>
     <t>范围伤害</t>
   </si>
   <si>
     <t>初始，另一个玩家打出也会取消</t>
   </si>
   <si>
+    <t>你可以撞伤怪物</t>
+  </si>
+  <si>
     <t>撞击怪物</t>
   </si>
   <si>
+    <t>怪物攻击肉体后，对自己造成等量伤害。持续3秒</t>
+  </si>
+  <si>
+    <t>反伤怪物</t>
+  </si>
+  <si>
     <t>反杀怪物</t>
   </si>
   <si>
+    <t>断裂</t>
+  </si>
+  <si>
+    <t>初始，推260像素</t>
+  </si>
+  <si>
+    <t>断裂。所有怪物往左推</t>
+  </si>
+  <si>
     <t>群体位移</t>
   </si>
   <si>
+    <t>获得10点血量</t>
+  </si>
+  <si>
     <t>恢复</t>
   </si>
   <si>
-    <t>断裂</t>
+    <t>移速翻倍</t>
+  </si>
+  <si>
+    <t>断裂。断裂时，移速增加</t>
   </si>
   <si>
     <t>加速</t>
@@ -83,24 +104,51 @@
     <t>B卡池</t>
   </si>
   <si>
+    <t>击退所有怪物，消耗血量</t>
+  </si>
+  <si>
     <t>击退</t>
   </si>
   <si>
+    <t>CD减少50%，持续7秒</t>
+  </si>
+  <si>
+    <t>断裂。玩家冷却加快</t>
+  </si>
+  <si>
     <t>CD分配</t>
   </si>
   <si>
+    <t>断裂。断裂时，冻结怪物</t>
+  </si>
+  <si>
     <t>群体冻结</t>
   </si>
   <si>
+    <t>持续7秒，还是有和其他东西的碰撞</t>
+  </si>
+  <si>
+    <t>肉体可以穿墙</t>
+  </si>
+  <si>
     <t>优化手牌</t>
   </si>
   <si>
     <t>也就是CD为0秒</t>
   </si>
   <si>
+    <t>断裂时，你无法出牌。队友没有CD</t>
+  </si>
+  <si>
     <t>集中火力</t>
   </si>
   <si>
+    <t>初始，增加1.5倍</t>
+  </si>
+  <si>
+    <t>队友下一次伤害增加</t>
+  </si>
+  <si>
     <t>增伤</t>
   </si>
   <si>
@@ -128,6 +176,9 @@
     <t>玩家的攻击可以移除弹幕</t>
   </si>
   <si>
+    <t>恢复牌：不在任何卡池：两个玩家开始时各持有一张：恢复链接，回满血</t>
+  </si>
+  <si>
     <t>敌人</t>
   </si>
   <si>
@@ -170,6 +221,9 @@
     <t>3秒一次</t>
   </si>
   <si>
+    <t>近战</t>
+  </si>
+  <si>
     <t>近战，类似冲击波</t>
   </si>
   <si>
@@ -255,95 +309,19 @@
   </si>
   <si>
     <t>转着圈射弹幕</t>
-  </si>
-  <si>
-    <t>击退所有怪物，消耗血量</t>
-  </si>
-  <si>
-    <t>连线对怪物造成伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断裂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断裂时，你无法出牌。队友没有CD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你可以撞伤怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断裂。断裂时，移速增加</t>
-  </si>
-  <si>
-    <t>获得10点血量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断裂。断裂时，冻结怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>队友下一次伤害增加</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始，增加1.5倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复牌：不在任何卡池：两个玩家开始时各持有一张：恢复链接，回满血</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>近战</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始，推260像素</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移速翻倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断裂。所有怪物往左推</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断裂。玩家冷却加快</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反伤怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪物攻击肉体后，对自己造成等量伤害。持续3秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CD减少50%，持续7秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>肉体可以穿墙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持续7秒，还是有和其他东西的碰撞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,30 +330,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -383,9 +683,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -393,24 +935,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -688,14 +1274,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
     <col min="3" max="3" width="21.625" customWidth="1"/>
@@ -705,12 +1291,12 @@
     <col min="9" max="9" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -727,7 +1313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="B3">
         <v>1</v>
       </c>
@@ -735,93 +1321,93 @@
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="J3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="B4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" spans="1:10">
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="J6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7">
         <v>5</v>
       </c>
       <c r="C7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12">
         <v>7</v>
       </c>
@@ -829,175 +1415,175 @@
         <v>6</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14">
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16">
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="B17">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="J17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="E18" s="1"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="C21" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="C22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="C23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="C24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="C25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="C26" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="C27" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="C28" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="G32" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H32" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I32" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="J32" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -1006,27 +1592,27 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="E33" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="H33" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J33" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -1035,15 +1621,15 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="I34" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -1052,27 +1638,27 @@
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E35" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G35" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="H35" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="J35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1081,15 +1667,15 @@
         <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -1098,30 +1684,30 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E37" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F37" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G37" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I37" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1130,75 +1716,75 @@
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F38" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="G38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E39" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F39" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="G39" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="J39" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="N39">
         <f>F3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="B41">
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G41" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="11_D2D259D325CD7DA1B49D6F7F5D4148009012F6B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8C6084F-4BBB-4C8A-A698-E081AF149CBF}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="11_D2D259D325CD7DA1B49D6F7F5D4148009012F6B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDDD2BAA-FD69-4F6D-8207-9B1FCDBBD97E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
   <si>
     <t>A卡池</t>
   </si>
@@ -204,6 +204,18 @@
   </si>
   <si>
     <t>初始，队友下一次伤害增加1.5倍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不正常，持续了超过7秒</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -291,6 +303,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -583,12 +599,12 @@
     <col min="9" max="9" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -604,8 +620,11 @@
       <c r="G2" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>1</v>
       </c>
@@ -618,8 +637,11 @@
       <c r="G3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>2</v>
       </c>
@@ -632,8 +654,11 @@
       <c r="G4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="H4" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>3</v>
       </c>
@@ -647,8 +672,9 @@
       <c r="G5" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>4</v>
       </c>
@@ -664,8 +690,11 @@
       <c r="G6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>5</v>
       </c>
@@ -677,7 +706,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>6</v>
       </c>
@@ -694,12 +723,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>7</v>
       </c>
@@ -712,8 +741,11 @@
       <c r="G12" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>8</v>
       </c>
@@ -730,7 +762,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>9</v>
       </c>
@@ -747,7 +779,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>10</v>
       </c>
@@ -761,8 +793,11 @@
       <c r="G15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>11</v>
       </c>
@@ -779,7 +814,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>12</v>
       </c>
@@ -792,11 +827,14 @@
       <c r="G17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H17" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="E18" s="1"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
         <v>14</v>
       </c>
@@ -804,37 +842,37 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="11_D2D259D325CD7DA1B49D6F7F5D4148009012F6B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDDD2BAA-FD69-4F6D-8207-9B1FCDBBD97E}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="11_D2D259D325CD7DA1B49D6F7F5D4148009012F6B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C35541D-5F90-4719-AAF3-2644CC840483}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>A卡池</t>
   </si>
@@ -216,6 +216,10 @@
   </si>
   <si>
     <t>不正常，持续了超过7秒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不正常。视觉效果持续了超过3秒，但实际效果只生效了较短时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -658,7 +662,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>3</v>
       </c>
@@ -672,7 +676,9 @@
       <c r="G5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B6">
@@ -705,6 +711,9 @@
       <c r="G7" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="H7" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8">
@@ -721,6 +730,9 @@
       </c>
       <c r="G8" t="s">
         <v>34</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="11_D2D259D325CD7DA1B49D6F7F5D4148009012F6B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C35541D-5F90-4719-AAF3-2644CC840483}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="11_D2D259D325CD7DA1B49D6F7F5D4148009012F6B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FB96074-E2CC-428C-A155-A2D9AF957481}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
   <si>
     <t>A卡池</t>
   </si>
@@ -167,10 +167,6 @@
     <t>冷却加速</t>
   </si>
   <si>
-    <t>CD减少50%，持续7秒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>切断锚链。断裂时，冻结怪物</t>
   </si>
   <si>
@@ -220,6 +216,14 @@
   </si>
   <si>
     <t>不正常。视觉效果持续了超过3秒，但实际效果只生效了较短时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有玩家CD减少50%，持续7秒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不正常。没有玩家的Cd减少</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -625,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -642,7 +646,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -659,7 +663,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -677,7 +681,7 @@
         <v>28</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -688,7 +692,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>29</v>
@@ -697,7 +701,7 @@
         <v>30</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -712,7 +716,7 @@
         <v>32</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -732,7 +736,7 @@
         <v>34</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -754,7 +758,7 @@
         <v>36</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -765,13 +769,16 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
         <v>40</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -782,13 +789,16 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" t="s">
         <v>42</v>
       </c>
-      <c r="G14" t="s">
-        <v>43</v>
+      <c r="H14" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -797,16 +807,16 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -817,13 +827,16 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>49</v>
+      <c r="H16" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
@@ -831,7 +844,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>12</v>
@@ -840,7 +853,7 @@
         <v>13</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="11_D2D259D325CD7DA1B49D6F7F5D4148009012F6B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FB96074-E2CC-428C-A155-A2D9AF957481}"/>
+  <xr:revisionPtr revIDLastSave="160" documentId="11_D2D259D325CD7DA1B49D6F7F5D4148009012F6B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E5ADDB2-59F3-4328-9897-511DBA3A97E1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,60 +170,62 @@
     <t>切断锚链。断裂时，冻结怪物</t>
   </si>
   <si>
+    <t>初始，将摄像机内的怪物向左推260像素</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>链接恢复前，场景里的所有怪物无法移动或攻击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续7秒，肉体还是保留和其他东西的碰撞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>切断锚链。断裂时，你无法出牌。队友没有CD</t>
+  </si>
+  <si>
+    <t>切断输出</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>也就是队友的CD为0秒，直到链接恢复</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始，队友下一次伤害增加1.5倍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不正常，持续了超过7秒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不正常。视觉效果持续了超过3秒，但实际效果只生效了较短时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有玩家CD减少50%，持续7秒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不正常。没有玩家的Cd减少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>切断冻结</t>
-  </si>
-  <si>
-    <t>初始，将摄像机内的怪物向左推260像素</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>链接恢复前，场景里的所有怪物无法移动或攻击</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>穿墙</t>
-  </si>
-  <si>
-    <t>持续7秒，肉体还是保留和其他东西的碰撞</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>切断锚链。断裂时，你无法出牌。队友没有CD</t>
-  </si>
-  <si>
-    <t>切断输出</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>也就是队友的CD为0秒，直到链接恢复</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始，队友下一次伤害增加1.5倍</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否正常</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>正常</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不正常，持续了超过7秒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不正常。视觉效果持续了超过3秒，但实际效果只生效了较短时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>所有玩家CD减少50%，持续7秒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不正常。没有玩家的Cd减少</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -629,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -646,7 +648,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -663,7 +665,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -681,7 +683,7 @@
         <v>28</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -692,7 +694,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>29</v>
@@ -701,7 +703,7 @@
         <v>30</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -716,7 +718,7 @@
         <v>32</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -736,7 +738,7 @@
         <v>34</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -758,7 +760,7 @@
         <v>36</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -769,7 +771,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>39</v>
@@ -778,7 +780,7 @@
         <v>40</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -789,16 +791,16 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G14" t="s">
-        <v>42</v>
+      <c r="G14" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -807,16 +809,16 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G15" t="s">
-        <v>45</v>
+      <c r="G15" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -827,16 +829,16 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
@@ -844,7 +846,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>12</v>
@@ -853,7 +855,7 @@
         <v>13</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">

--- a/doc/2026CGJ卡牌设计新.xlsx
+++ b/doc/2026CGJ卡牌设计新.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="11_D2D259D325CD7DA1B49D6F7F5D4148009012F6B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E5ADDB2-59F3-4328-9897-511DBA3A97E1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23145" windowHeight="8955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>A卡池</t>
   </si>
@@ -44,33 +38,120 @@
     <t>词条</t>
   </si>
   <si>
+    <t>备注和具体数值</t>
+  </si>
+  <si>
     <t>内容</t>
   </si>
   <si>
+    <t>简介</t>
+  </si>
+  <si>
+    <t>初始，每个怪物5点伤害</t>
+  </si>
+  <si>
+    <t>锚线对怪物造成伤害</t>
+  </si>
+  <si>
     <t>范围伤害</t>
   </si>
   <si>
+    <t>初始，每次撞击4点伤害</t>
+  </si>
+  <si>
     <t>你可以撞伤怪物</t>
   </si>
   <si>
     <t>撞击怪物</t>
   </si>
   <si>
+    <t>怪物攻击肉体后，对自己造成等量伤害。持续3秒</t>
+  </si>
+  <si>
     <t>反伤怪物</t>
   </si>
   <si>
+    <t>反伤</t>
+  </si>
+  <si>
     <t>断裂</t>
   </si>
   <si>
+    <t>将摄像机内的怪物向左推260像素</t>
+  </si>
+  <si>
+    <t>切断锚链。所有怪物往左推</t>
+  </si>
+  <si>
+    <t>切断位移</t>
+  </si>
+  <si>
+    <t>回10点血</t>
+  </si>
+  <si>
+    <t>回血</t>
+  </si>
+  <si>
+    <t>移速增加100%</t>
+  </si>
+  <si>
+    <t>切断锚链。断裂时，移速增加</t>
+  </si>
+  <si>
+    <t>切断加速</t>
+  </si>
+  <si>
     <t>B卡池</t>
   </si>
   <si>
+    <t>初始，失去4点血量</t>
+  </si>
+  <si>
     <t>击退所有怪物，消耗血量</t>
   </si>
   <si>
+    <t>失血击退</t>
+  </si>
+  <si>
+    <t>所有玩家CD减少50%，持续7秒</t>
+  </si>
+  <si>
+    <t>切断锚链。冷却加快</t>
+  </si>
+  <si>
+    <t>冷却加速</t>
+  </si>
+  <si>
+    <t>链接恢复前，场景里的所有怪物无法移动或攻击</t>
+  </si>
+  <si>
+    <t>切断锚链。断裂时，冻结怪物</t>
+  </si>
+  <si>
+    <t>切断冻结</t>
+  </si>
+  <si>
+    <t>持续7秒，肉体还是保留和其他东西的碰撞</t>
+  </si>
+  <si>
     <t>肉体可以穿墙</t>
   </si>
   <si>
+    <t>穿墙</t>
+  </si>
+  <si>
+    <t>也就是队友的CD为0秒，直到链接恢复</t>
+  </si>
+  <si>
+    <t>切断锚链。断裂时，你无法出牌。队友没有CD</t>
+  </si>
+  <si>
+    <t>切断输出</t>
+  </si>
+  <si>
+    <t>初始，队友下一次伤害增加1.5倍</t>
+  </si>
+  <si>
     <t>队友下一次伤害增加</t>
   </si>
   <si>
@@ -102,138 +183,19 @@
   </si>
   <si>
     <t>恢复牌：不在任何卡池：两个玩家开始时各持有一张：恢复链接，回满血</t>
-  </si>
-  <si>
-    <t>简介</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>锚线对怪物造成伤害</t>
-  </si>
-  <si>
-    <t>初始，每个怪物5点伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始，每次撞击4点伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪物攻击肉体后，对自己造成等量伤害。持续3秒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>反伤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>切断锚链。所有怪物往左推</t>
-  </si>
-  <si>
-    <t>切断位移</t>
-  </si>
-  <si>
-    <t>回10点血</t>
-  </si>
-  <si>
-    <t>回血</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>切断锚链。断裂时，移速增加</t>
-  </si>
-  <si>
-    <t>切断加速</t>
-  </si>
-  <si>
-    <t>移速增加100%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>失血击退</t>
-  </si>
-  <si>
-    <t>初始，失去4点血量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注和具体数值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>切断锚链。冷却加快</t>
-  </si>
-  <si>
-    <t>冷却加速</t>
-  </si>
-  <si>
-    <t>切断锚链。断裂时，冻结怪物</t>
-  </si>
-  <si>
-    <t>初始，将摄像机内的怪物向左推260像素</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>链接恢复前，场景里的所有怪物无法移动或攻击</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>持续7秒，肉体还是保留和其他东西的碰撞</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>切断锚链。断裂时，你无法出牌。队友没有CD</t>
-  </si>
-  <si>
-    <t>切断输出</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>也就是队友的CD为0秒，直到链接恢复</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始，队友下一次伤害增加1.5倍</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否正常</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>正常</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不正常，持续了超过7秒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不正常。视觉效果持续了超过3秒，但实际效果只生效了较短时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>所有玩家CD减少50%，持续7秒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不正常。没有玩家的Cd减少</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>切断冻结</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>穿墙</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,29 +211,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -279,9 +557,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -292,31 +812,71 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -591,14 +1151,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
     <col min="3" max="3" width="21.625" customWidth="1"/>
@@ -609,312 +1169,286 @@
     <col min="9" max="9" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>38</v>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8">
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>24</v>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8">
       <c r="B4">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" ht="48.75" customHeight="1" spans="1:8">
       <c r="B5">
         <v>3</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="2"/>
       <c r="D5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8">
       <c r="B6">
         <v>4</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>29</v>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8">
       <c r="B7">
         <v>5</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="B12">
         <v>7</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>10</v>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8">
       <c r="B13">
         <v>8</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>39</v>
+      <c r="C13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="B14">
         <v>9</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="B15">
         <v>10</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C15" s="2"/>
+      <c r="D15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8">
       <c r="B16">
         <v>11</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="2:8">
       <c r="B17">
         <v>12</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="C22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="C24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="C25" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="2" t="s">
+    </row>
+    <row r="26" spans="2:8">
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="C27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="E18" s="1"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C28" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="7:14" x14ac:dyDescent="0.2">
-      <c r="G33" s="1"/>
-    </row>
-    <row r="39" spans="7:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:8">
+      <c r="C28" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="7:14">
+      <c r="G33" s="2"/>
+    </row>
+    <row r="39" spans="7:14">
       <c r="N39">
         <f>F3</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>